--- a/s2022_280k_lambda_sweep_cv.xlsx
+++ b/s2022_280k_lambda_sweep_cv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mitra\Downloads\matlab analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4671E1C9-0457-4740-84B4-7F96F53D2DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF5C5222-D1CC-4891-8C06-6C76070C6A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{E1838CA4-D4E5-463E-8E25-DE1439AC94FC}"/>
   </bookViews>
@@ -39,21 +39,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>selected_temperature_K</t>
   </si>
   <si>
-    <t>resid_diff_pct_1e4_vs_1e3</t>
-  </si>
-  <si>
-    <t>small_diff_threshold_pct</t>
-  </si>
-  <si>
     <t>selected_cv_lambda</t>
-  </si>
-  <si>
-    <t>used_1e3_flag</t>
   </si>
   <si>
     <t>lambda</t>
@@ -120,6 +111,30 @@
   </si>
   <si>
     <t>gamma_cv_run_5_lambda_1e3</t>
+  </si>
+  <si>
+    <t>cv_boundary_low_idx</t>
+  </si>
+  <si>
+    <t>cv_boundary_high_idx</t>
+  </si>
+  <si>
+    <t>selected_lambda_index</t>
+  </si>
+  <si>
+    <t>RID</t>
+  </si>
+  <si>
+    <t>CV_real</t>
+  </si>
+  <si>
+    <t>CV_imag</t>
+  </si>
+  <si>
+    <t>resample_variance</t>
+  </si>
+  <si>
+    <t>score</t>
   </si>
 </sst>
 </file>
@@ -488,16 +503,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -505,16 +520,16 @@
         <v>280.33999999999997</v>
       </c>
       <c r="B2">
-        <v>1.2968685704625726</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>1E-3</v>
+        <v>0.1</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -524,33 +539,48 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F70D3F7B-4DE4-4635-8042-A65E57D6517D}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1E-4</v>
       </c>
@@ -572,8 +602,23 @@
       <c r="G2">
         <v>170.42443338913861</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2">
+        <v>809672.33605630288</v>
+      </c>
+      <c r="I2">
+        <v>5852.2810124737616</v>
+      </c>
+      <c r="J2">
+        <v>44901.711105867558</v>
+      </c>
+      <c r="K2">
+        <v>25880.870233002184</v>
+      </c>
+      <c r="L2">
+        <v>2.0437161930460555</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1E-3</v>
       </c>
@@ -595,8 +640,23 @@
       <c r="G3">
         <v>81.632954962841623</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3">
+        <v>147676.96040997337</v>
+      </c>
+      <c r="I3">
+        <v>5839.6365707591021</v>
+      </c>
+      <c r="J3">
+        <v>44567.165734492817</v>
+      </c>
+      <c r="K3">
+        <v>2560.103737232489</v>
+      </c>
+      <c r="L3">
+        <v>0.28782793221724479</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -618,8 +678,23 @@
       <c r="G4">
         <v>101.61162006253835</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>48942.379747524406</v>
+      </c>
+      <c r="I4">
+        <v>5896.9253748401279</v>
+      </c>
+      <c r="J4">
+        <v>44221.271252902792</v>
+      </c>
+      <c r="K4">
+        <v>1328.3588202975309</v>
+      </c>
+      <c r="L4">
+        <v>9.6656786769258707E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>0.01</v>
       </c>
@@ -641,8 +716,23 @@
       <c r="G5">
         <v>89.580286063093482</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>32540.311422796454</v>
+      </c>
+      <c r="I5">
+        <v>6110.079811136944</v>
+      </c>
+      <c r="J5">
+        <v>44204.063769531946</v>
+      </c>
+      <c r="K5">
+        <v>465.6990691847306</v>
+      </c>
+      <c r="L5">
+        <v>5.6184983817103296E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>0.1</v>
       </c>
@@ -663,6 +753,21 @@
       </c>
       <c r="G6">
         <v>87.571065930142396</v>
+      </c>
+      <c r="H6">
+        <v>11017.899067739954</v>
+      </c>
+      <c r="I6">
+        <v>17517.036223604231</v>
+      </c>
+      <c r="J6">
+        <v>47144.867124634409</v>
+      </c>
+      <c r="K6">
+        <v>58.646034221302898</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -677,16 +782,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -694,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>64.600761839634401</v>
+        <v>81.545635955710665</v>
       </c>
       <c r="C2">
-        <v>82.378499864147201</v>
+        <v>98.560562186295655</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -708,13 +813,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>69.565324607929895</v>
+        <v>83.477433021315932</v>
       </c>
       <c r="C3">
-        <v>58.606566277488</v>
+        <v>70.363738830079981</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -722,13 +827,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>74.233450997621759</v>
+        <v>87.946526467432918</v>
       </c>
       <c r="C4">
-        <v>37.235578172964281</v>
+        <v>53.184073901675525</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -736,13 +841,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>57.246977376599865</v>
+        <v>75.0818226238233</v>
       </c>
       <c r="C5">
-        <v>122.92026375485145</v>
+        <v>137.45239124251847</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -750,13 +855,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>75.953603099876631</v>
+        <v>86.196971432601131</v>
       </c>
       <c r="C6">
-        <v>24.558530411415934</v>
+        <v>37.24513383856015</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -771,22 +876,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -4761,22 +4866,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
